--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Different Folder\Code\python\Restart\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Different Folder\Code\python\Scrapping the Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{45BF5146-6730-48EC-AE8E-03F28AA10B93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{197FBBB1-34D8-4AA6-A90A-8F36C8B19743}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{43B1A38A-3033-4D74-9A5B-D8150D859200}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Column1</t>
   </si>
@@ -47,6 +47,9 @@
   </si>
   <si>
     <t>sdgds</t>
+  </si>
+  <si>
+    <t>hey there 123</t>
   </si>
 </sst>
 </file>
@@ -887,7 +890,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF7CBE47-948E-4BB6-A314-2175197FA50D}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
@@ -923,6 +926,14 @@
         <v>8</v>
       </c>
     </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="B4">
+        <v>123</v>
+      </c>
+      <c r="C4" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
